--- a/data/trans_orig/Q5412-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5412-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de arreglarse en 2007</t>
+          <t>Población según si es capaz de arreglarse en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>987</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16825</t>
+          <t>17204</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103084</t>
+          <t>101959</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112323</t>
+          <t>112185</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140437</t>
+          <t>140594</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>148538</t>
+          <t>148548</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>247699</t>
+          <t>247320</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>259756</t>
+          <t>259746</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19604</t>
+          <t>21183</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24829</t>
+          <t>26006</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>135525</t>
+          <t>135168</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>144017</t>
+          <t>144062</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>163076</t>
+          <t>161497</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>177360</t>
+          <t>177131</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>303739</t>
+          <t>302562</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>320408</t>
+          <t>320064</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>11743</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13320</t>
+          <t>13732</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>99365</t>
+          <t>99466</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122700</t>
+          <t>124107</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133111</t>
+          <t>133791</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>226901</t>
+          <t>226489</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>237249</t>
+          <t>237116</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>828</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14223</t>
+          <t>14180</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5417</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18458</t>
+          <t>17546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>129715</t>
+          <t>129719</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>136405</t>
+          <t>136389</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>194554</t>
+          <t>194597</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>205542</t>
+          <t>205785</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>327537</t>
+          <t>328449</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>340578</t>
+          <t>341176</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23913</t>
+          <t>23707</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18436</t>
+          <t>18336</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40086</t>
+          <t>39283</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31886</t>
+          <t>32339</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56551</t>
+          <t>57103</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>478553</t>
+          <t>478759</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>493346</t>
+          <t>492669</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>636756</t>
+          <t>637559</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>658406</t>
+          <t>658506</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1122757</t>
+          <t>1122205</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1147422</t>
+          <t>1146969</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de arreglarse en 2012</t>
+          <t>Población según si es capaz de arreglarse en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>11314</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23546</t>
+          <t>24480</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>13066</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30226</t>
+          <t>30154</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>128484</t>
+          <t>128233</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>138432</t>
+          <t>137463</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>143241</t>
+          <t>142307</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>158329</t>
+          <t>157390</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276108</t>
+          <t>276180</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>293463</t>
+          <t>293268</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21620</t>
+          <t>21541</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18594</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37168</t>
+          <t>36446</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28557</t>
+          <t>28198</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54499</t>
+          <t>51712</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>133258</t>
+          <t>133337</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>148412</t>
+          <t>147563</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>154252</t>
+          <t>154974</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>172826</t>
+          <t>173716</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>291799</t>
+          <t>294586</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>317741</t>
+          <t>318100</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16028</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29776</t>
+          <t>29055</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17383</t>
+          <t>18134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>40730</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87570</t>
+          <t>87400</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100497</t>
+          <t>100433</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111243</t>
+          <t>111964</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129090</t>
+          <t>129442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>204888</t>
+          <t>203887</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>227234</t>
+          <t>226483</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17522</t>
+          <t>17211</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10310</t>
+          <t>10475</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27844</t>
+          <t>27889</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18110</t>
+          <t>17548</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39370</t>
+          <t>38874</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>144091</t>
+          <t>144402</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>157688</t>
+          <t>157481</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>215906</t>
+          <t>215861</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>233440</t>
+          <t>233275</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>365993</t>
+          <t>366489</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>387253</t>
+          <t>387815</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25195</t>
+          <t>23922</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49738</t>
+          <t>47916</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62944</t>
+          <t>63076</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97162</t>
+          <t>96953</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93666</t>
+          <t>93682</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>137205</t>
+          <t>137367</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>509899</t>
+          <t>511721</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>534442</t>
+          <t>535715</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>645813</t>
+          <t>646022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>680031</t>
+          <t>679899</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1165407</t>
+          <t>1165245</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1208946</t>
+          <t>1208930</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de arreglarse en 2016</t>
+          <t>Población según si es capaz de arreglarse en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13995</t>
+          <t>14003</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22436</t>
+          <t>22375</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13210</t>
+          <t>12950</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31726</t>
+          <t>30886</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>122739</t>
+          <t>122731</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133184</t>
+          <t>133197</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>150955</t>
+          <t>151016</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>166359</t>
+          <t>166416</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>278399</t>
+          <t>279239</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>296915</t>
+          <t>297175</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>2464</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>10747</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24299</t>
+          <t>24555</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29818</t>
+          <t>32686</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154434</t>
+          <t>154194</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163177</t>
+          <t>162477</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>194864</t>
+          <t>194608</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>211533</t>
+          <t>211896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>354286</t>
+          <t>351418</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>372604</t>
+          <t>372998</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12466</t>
+          <t>12238</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>22002</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29013</t>
+          <t>29607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102569</t>
+          <t>102797</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112852</t>
+          <t>112917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120014</t>
+          <t>120594</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135496</t>
+          <t>135491</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>228618</t>
+          <t>228024</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>245912</t>
+          <t>245710</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>758</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24216</t>
+          <t>23508</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27693</t>
+          <t>26500</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166921</t>
+          <t>166419</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>173851</t>
+          <t>173860</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>218565</t>
+          <t>219273</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>236633</t>
+          <t>236362</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>389707</t>
+          <t>390900</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>409033</t>
+          <t>408648</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14694</t>
+          <t>14280</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>32597</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38174</t>
+          <t>39457</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71489</t>
+          <t>72401</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57097</t>
+          <t>59214</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93436</t>
+          <t>94845</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>558757</t>
+          <t>558731</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>576634</t>
+          <t>577048</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>706442</t>
+          <t>705530</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>739757</t>
+          <t>738474</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1275823</t>
+          <t>1274414</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1312162</t>
+          <t>1310045</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de arreglarse en 2023</t>
+          <t>Población según si es capaz de arreglarse en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15760</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>18628</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30510</t>
+          <t>30511</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27614</t>
+          <t>28101</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43476</t>
+          <t>43065</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132323</t>
+          <t>131497</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>141543</t>
+          <t>141690</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>148653</t>
+          <t>148652</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>160648</t>
+          <t>160535</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>283770</t>
+          <t>284181</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>299632</t>
+          <t>299145</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,41%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13693</t>
+          <t>14740</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17749</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30825</t>
+          <t>32371</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25745</t>
+          <t>25198</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41251</t>
+          <t>41644</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>146421</t>
+          <t>145374</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155287</t>
+          <t>154630</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>187570</t>
+          <t>186024</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>200646</t>
+          <t>200372</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>337258</t>
+          <t>336865</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>352764</t>
+          <t>353311</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39232</t>
+          <t>37806</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34220</t>
+          <t>35133</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>128389</t>
+          <t>128187</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135502</t>
+          <t>135656</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>321024</t>
+          <t>322450</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>357059</t>
+          <t>356606</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>462989</t>
+          <t>462076</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>492153</t>
+          <t>491257</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13921</t>
+          <t>13716</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13093</t>
+          <t>12994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25602</t>
+          <t>25159</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20437</t>
+          <t>20403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35106</t>
+          <t>35075</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>191108</t>
+          <t>191313</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200565</t>
+          <t>200373</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>250021</t>
+          <t>250464</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>262530</t>
+          <t>262629</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>445547</t>
+          <t>445578</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>460216</t>
+          <t>460250</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22856</t>
+          <t>23719</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40662</t>
+          <t>40976</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41801</t>
+          <t>40880</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106782</t>
+          <t>106382</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77602</t>
+          <t>74508</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136556</t>
+          <t>135928</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>609516</t>
+          <t>609202</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>627322</t>
+          <t>626459</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>926656</t>
+          <t>927056</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>991637</t>
+          <t>992558</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1547061</t>
+          <t>1547689</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1606015</t>
+          <t>1609109</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5412-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5412-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8941</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17204</t>
+          <t>17050</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101959</t>
+          <t>102946</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112185</t>
+          <t>112254</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>140594</t>
+          <t>140390</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>148548</t>
+          <t>148532</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>247320</t>
+          <t>247474</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>259746</t>
+          <t>259824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10721</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21183</t>
+          <t>19381</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26006</t>
+          <t>25840</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>135168</t>
+          <t>135450</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>144062</t>
+          <t>144054</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>161497</t>
+          <t>163299</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>177131</t>
+          <t>177219</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>302562</t>
+          <t>302728</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>320064</t>
+          <t>319308</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2274</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11743</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13732</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>99466</t>
+          <t>99425</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>124107</t>
+          <t>123276</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133791</t>
+          <t>133576</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>226489</t>
+          <t>226631</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>237116</t>
+          <t>237246</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7522</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14180</t>
+          <t>13994</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17546</t>
+          <t>18251</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>129719</t>
+          <t>129695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>136389</t>
+          <t>136394</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>194597</t>
+          <t>194783</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>205785</t>
+          <t>205740</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>328449</t>
+          <t>327744</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>341176</t>
+          <t>340449</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23707</t>
+          <t>24848</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18336</t>
+          <t>18554</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39283</t>
+          <t>40174</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32339</t>
+          <t>31094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57103</t>
+          <t>57075</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>478759</t>
+          <t>477618</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>492669</t>
+          <t>492565</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>637559</t>
+          <t>636668</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>658506</t>
+          <t>658288</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1122205</t>
+          <t>1122233</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1146969</t>
+          <t>1148214</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11314</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9397</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24480</t>
+          <t>24124</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>12649</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30154</t>
+          <t>30541</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>128233</t>
+          <t>128636</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137463</t>
+          <t>138413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>142307</t>
+          <t>142663</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>157390</t>
+          <t>158177</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276180</t>
+          <t>275793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>293268</t>
+          <t>293685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>7379</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21541</t>
+          <t>21841</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17704</t>
+          <t>18043</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36446</t>
+          <t>37011</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28198</t>
+          <t>28277</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51712</t>
+          <t>52528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>133337</t>
+          <t>133037</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>147563</t>
+          <t>147499</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>154974</t>
+          <t>154409</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>173716</t>
+          <t>173377</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>294586</t>
+          <t>293770</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>318100</t>
+          <t>318021</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>15975</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11577</t>
+          <t>11536</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29055</t>
+          <t>29487</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18134</t>
+          <t>17913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40730</t>
+          <t>38878</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87400</t>
+          <t>87623</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100433</t>
+          <t>100516</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111964</t>
+          <t>111532</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129442</t>
+          <t>129483</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>203887</t>
+          <t>205739</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>226483</t>
+          <t>226704</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17211</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27889</t>
+          <t>28582</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>17321</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38874</t>
+          <t>39086</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>144402</t>
+          <t>143286</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>157481</t>
+          <t>157485</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>215861</t>
+          <t>215168</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>233275</t>
+          <t>233201</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>366489</t>
+          <t>366277</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>387815</t>
+          <t>388042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23922</t>
+          <t>23993</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47916</t>
+          <t>47952</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63076</t>
+          <t>60690</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96953</t>
+          <t>96024</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93682</t>
+          <t>94263</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>137367</t>
+          <t>135784</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>511721</t>
+          <t>511685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>535715</t>
+          <t>535644</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>646022</t>
+          <t>646951</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>679899</t>
+          <t>682285</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1165245</t>
+          <t>1166828</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1208930</t>
+          <t>1208349</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14003</t>
+          <t>14341</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22375</t>
+          <t>20775</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>13139</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30886</t>
+          <t>30677</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>122731</t>
+          <t>122393</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133197</t>
+          <t>132653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151016</t>
+          <t>152616</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>166416</t>
+          <t>166494</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>279239</t>
+          <t>279448</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>297175</t>
+          <t>296986</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10747</t>
+          <t>10959</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24555</t>
+          <t>25523</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11106</t>
+          <t>11294</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32686</t>
+          <t>30538</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154194</t>
+          <t>153982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>162477</t>
+          <t>162434</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>194608</t>
+          <t>193640</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>211896</t>
+          <t>211660</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>351418</t>
+          <t>353566</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>372998</t>
+          <t>372810</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12238</t>
+          <t>12495</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22002</t>
+          <t>22532</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11921</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29607</t>
+          <t>30901</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102797</t>
+          <t>102540</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112917</t>
+          <t>112841</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120594</t>
+          <t>120064</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135491</t>
+          <t>135238</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>228024</t>
+          <t>226730</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>245710</t>
+          <t>246102</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23508</t>
+          <t>23976</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26500</t>
+          <t>27266</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166419</t>
+          <t>166095</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>173860</t>
+          <t>174618</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>219273</t>
+          <t>218805</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>236362</t>
+          <t>236421</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>390900</t>
+          <t>390134</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>408648</t>
+          <t>409156</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14280</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32597</t>
+          <t>30937</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39457</t>
+          <t>38867</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72401</t>
+          <t>72647</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59214</t>
+          <t>58349</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94845</t>
+          <t>95326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>558731</t>
+          <t>560391</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>577048</t>
+          <t>577316</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>705530</t>
+          <t>705284</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>738474</t>
+          <t>739064</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1274414</t>
+          <t>1273933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1310045</t>
+          <t>1310910</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10534</t>
+          <t>11177</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16586</t>
+          <t>17053</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>25543</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18628</t>
+          <t>19070</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30511</t>
+          <t>32298</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>34779</t>
+          <t>36720</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28101</t>
+          <t>29095</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43065</t>
+          <t>45219</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>137549</t>
+          <t>152137</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131497</t>
+          <t>146261</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>141690</t>
+          <t>156799</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>154918</t>
+          <t>165486</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>148652</t>
+          <t>158731</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>160535</t>
+          <t>171959</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>292467</t>
+          <t>317623</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284181</t>
+          <t>309124</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>299145</t>
+          <t>325248</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14740</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23919</t>
+          <t>25212</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18023</t>
+          <t>19222</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32371</t>
+          <t>33497</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>32681</t>
+          <t>34443</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25198</t>
+          <t>26484</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41644</t>
+          <t>43852</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>151352</t>
+          <t>168973</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>145374</t>
+          <t>163041</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154630</t>
+          <t>173050</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>194476</t>
+          <t>216450</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>186024</t>
+          <t>208165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>200372</t>
+          <t>222440</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>345828</t>
+          <t>385423</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>336865</t>
+          <t>376014</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>353311</t>
+          <t>393382</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>218395</t>
+          <t>241662</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>218395</t>
+          <t>241662</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>218395</t>
+          <t>241662</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>378509</t>
+          <t>419866</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>378509</t>
+          <t>419866</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>378509</t>
+          <t>419866</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14937</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37806</t>
+          <t>22847</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18798</t>
+          <t>20299</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35133</t>
+          <t>28420</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>133091</t>
+          <t>155433</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>128187</t>
+          <t>150660</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135656</t>
+          <t>158143</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>345319</t>
+          <t>158963</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>322450</t>
+          <t>152062</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>356606</t>
+          <t>165007</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>478411</t>
+          <t>314395</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>462076</t>
+          <t>306274</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>491257</t>
+          <t>320474</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13716</t>
+          <t>14460</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18680</t>
+          <t>20582</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>14434</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25159</t>
+          <t>28067</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>27029</t>
+          <t>29456</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35075</t>
+          <t>38223</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>196681</t>
+          <t>206215</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>191313</t>
+          <t>200629</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200373</t>
+          <t>210163</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>256943</t>
+          <t>274784</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>250464</t>
+          <t>267299</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>262629</t>
+          <t>280932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>453624</t>
+          <t>480998</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>445578</t>
+          <t>472231</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>460250</t>
+          <t>489044</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>31505</t>
+          <t>33634</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23719</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40976</t>
+          <t>44026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>81781</t>
+          <t>87283</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40880</t>
+          <t>75369</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106382</t>
+          <t>100912</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>113286</t>
+          <t>120918</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74508</t>
+          <t>106059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135928</t>
+          <t>138105</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>618673</t>
+          <t>682757</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>609202</t>
+          <t>672365</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>626459</t>
+          <t>691451</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>951657</t>
+          <t>815683</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>927056</t>
+          <t>802054</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>992558</t>
+          <t>827597</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1570331</t>
+          <t>1498439</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1547689</t>
+          <t>1481252</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1609109</t>
+          <t>1513298</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1033438</t>
+          <t>902966</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1033438</t>
+          <t>902966</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1033438</t>
+          <t>902966</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1683617</t>
+          <t>1619357</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1683617</t>
+          <t>1619357</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1683617</t>
+          <t>1619357</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
